--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/27,08,26 ПОКОМ КИ/дв 27,08,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/27,08,26 ПОКОМ КИ/дв 27,08,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\27,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9189AED8-A1EC-47EE-A4E6-263A90A02268}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBA001A-4F3F-425D-9ABD-187561BCED44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$134</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -762,7 +754,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -776,7 +768,6 @@
     <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -801,7 +792,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -6603,7 +6594,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="18">
+      <c r="U1" s="17">
         <v>0.7</v>
       </c>
       <c r="V1" s="1"/>
@@ -7385,7 +7376,7 @@
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="5">
-        <f t="shared" ref="U7:U66" si="8">T9</f>
+        <f t="shared" ref="U9:U66" si="8">T9</f>
         <v>0</v>
       </c>
       <c r="V9" s="1" t="e">
@@ -7805,7 +7796,7 @@
       <c r="H13" s="1">
         <v>40</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J13" s="1"/>
@@ -8905,7 +8896,7 @@
       <c r="H23" s="1">
         <v>70</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="1"/>
@@ -9116,7 +9107,7 @@
       <c r="H25" s="1">
         <v>70</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="1"/>
@@ -9229,7 +9220,7 @@
       <c r="H26" s="1">
         <v>40</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="1"/>
@@ -9450,7 +9441,7 @@
       <c r="H28" s="1">
         <v>40</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="1"/>
@@ -9564,7 +9555,7 @@
       <c r="H29" s="1">
         <v>30</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J29" s="1"/>
@@ -9886,7 +9877,7 @@
       <c r="H32" s="1">
         <v>40</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J32" s="1"/>
@@ -10099,7 +10090,7 @@
       <c r="H34" s="1">
         <v>30</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J34" s="1"/>
@@ -10407,7 +10398,7 @@
       <c r="H37" s="1">
         <v>45</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J37" s="1"/>
@@ -10632,7 +10623,7 @@
       <c r="H39" s="1">
         <v>45</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J39" s="1"/>
@@ -10720,7 +10711,7 @@
       <c r="AU39" s="1"/>
     </row>
     <row r="40" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -10738,7 +10729,7 @@
       <c r="H40" s="1">
         <v>40</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J40" s="1"/>
@@ -10850,7 +10841,7 @@
       <c r="H41" s="1">
         <v>45</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J41" s="1"/>
@@ -11071,7 +11062,7 @@
       <c r="H43" s="1">
         <v>40</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J43" s="1"/>
@@ -11185,7 +11176,7 @@
       <c r="H44" s="1">
         <v>40</v>
       </c>
-      <c r="I44" s="14" t="s">
+      <c r="I44" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J44" s="1"/>
@@ -11299,7 +11290,7 @@
       <c r="H45" s="1">
         <v>40</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J45" s="1"/>
@@ -11411,7 +11402,7 @@
       <c r="H46" s="1">
         <v>45</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J46" s="1"/>
@@ -11523,7 +11514,7 @@
       <c r="H47" s="1">
         <v>40</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J47" s="1"/>
@@ -11633,7 +11624,7 @@
       <c r="H48" s="1">
         <v>40</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="I48" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J48" s="1"/>
@@ -11747,7 +11738,7 @@
       <c r="H49" s="1">
         <v>40</v>
       </c>
-      <c r="I49" s="14" t="s">
+      <c r="I49" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J49" s="1"/>
@@ -12082,7 +12073,7 @@
       <c r="H52" s="1">
         <v>45</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J52" s="1"/>
@@ -12151,7 +12142,7 @@
       <c r="AG52" s="1">
         <v>11.0654</v>
       </c>
-      <c r="AH52" s="15" t="s">
+      <c r="AH52" s="14" t="s">
         <v>126</v>
       </c>
       <c r="AI52" s="1">
@@ -12416,7 +12407,7 @@
       <c r="H55" s="1">
         <v>40</v>
       </c>
-      <c r="I55" s="14" t="s">
+      <c r="I55" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J55" s="1"/>
@@ -12530,7 +12521,7 @@
       <c r="H56" s="1">
         <v>40</v>
       </c>
-      <c r="I56" s="14" t="s">
+      <c r="I56" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J56" s="1"/>
@@ -13484,7 +13475,7 @@
       <c r="AG64" s="1">
         <v>9.9244000000000003</v>
       </c>
-      <c r="AH64" s="17" t="s">
+      <c r="AH64" s="16" t="s">
         <v>104</v>
       </c>
       <c r="AI64" s="1">
@@ -13751,7 +13742,7 @@
       <c r="H67" s="1">
         <v>40</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J67" s="1"/>
@@ -13864,7 +13855,7 @@
       <c r="H68" s="1">
         <v>40</v>
       </c>
-      <c r="I68" s="14" t="s">
+      <c r="I68" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J68" s="1"/>
@@ -13978,7 +13969,7 @@
       <c r="H69" s="1">
         <v>40</v>
       </c>
-      <c r="I69" s="14" t="s">
+      <c r="I69" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J69" s="1"/>
@@ -14092,7 +14083,7 @@
       <c r="H70" s="1">
         <v>40</v>
       </c>
-      <c r="I70" s="14" t="s">
+      <c r="I70" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J70" s="1"/>
@@ -14206,7 +14197,7 @@
       <c r="H71" s="1">
         <v>40</v>
       </c>
-      <c r="I71" s="14" t="s">
+      <c r="I71" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J71" s="1"/>
@@ -14869,7 +14860,7 @@
       <c r="H77" s="1">
         <v>60</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J77" s="1"/>
@@ -15377,7 +15368,7 @@
       <c r="AG81" s="1">
         <v>8.6</v>
       </c>
-      <c r="AH81" s="15" t="s">
+      <c r="AH81" s="14" t="s">
         <v>126</v>
       </c>
       <c r="AI81" s="1">
@@ -15533,7 +15524,7 @@
       <c r="H83" s="1">
         <v>40</v>
       </c>
-      <c r="I83" s="14" t="s">
+      <c r="I83" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J83" s="1"/>
@@ -16951,7 +16942,7 @@
       <c r="H96" s="1">
         <v>40</v>
       </c>
-      <c r="I96" s="14" t="s">
+      <c r="I96" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J96" s="1"/>
@@ -17274,7 +17265,7 @@
       <c r="H99" s="1">
         <v>90</v>
       </c>
-      <c r="I99" s="14" t="s">
+      <c r="I99" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J99" s="1"/>
@@ -17607,7 +17598,7 @@
       <c r="H102" s="1">
         <v>40</v>
       </c>
-      <c r="I102" s="14" t="s">
+      <c r="I102" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J102" s="1"/>
@@ -17717,7 +17708,7 @@
       <c r="H103" s="1">
         <v>55</v>
       </c>
-      <c r="I103" s="14" t="s">
+      <c r="I103" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J103" s="1"/>
@@ -18320,7 +18311,7 @@
       <c r="AG108" s="1">
         <v>0.4</v>
       </c>
-      <c r="AH108" s="16" t="s">
+      <c r="AH108" s="15" t="s">
         <v>179</v>
       </c>
       <c r="AI108" s="1">
@@ -18365,7 +18356,7 @@
       <c r="H109" s="1">
         <v>40</v>
       </c>
-      <c r="I109" s="14" t="s">
+      <c r="I109" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J109" s="1"/>
@@ -18477,7 +18468,7 @@
       <c r="H110" s="1">
         <v>40</v>
       </c>
-      <c r="I110" s="14" t="s">
+      <c r="I110" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J110" s="1"/>
@@ -18589,7 +18580,7 @@
       <c r="H111" s="1">
         <v>40</v>
       </c>
-      <c r="I111" s="14" t="s">
+      <c r="I111" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J111" s="1"/>
@@ -18867,7 +18858,7 @@
       <c r="AG113" s="1">
         <v>0.28160000000000002</v>
       </c>
-      <c r="AH113" s="17" t="s">
+      <c r="AH113" s="16" t="s">
         <v>180</v>
       </c>
       <c r="AI113" s="1">
@@ -19118,7 +19109,7 @@
       <c r="H116" s="1">
         <v>40</v>
       </c>
-      <c r="I116" s="14" t="s">
+      <c r="I116" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J116" s="1"/>
@@ -19515,7 +19506,7 @@
       <c r="AG119" s="1">
         <v>15.0108</v>
       </c>
-      <c r="AH119" s="15" t="s">
+      <c r="AH119" s="14" t="s">
         <v>126</v>
       </c>
       <c r="AI119" s="1">
@@ -20215,7 +20206,7 @@
         <v>0.25</v>
       </c>
       <c r="H126" s="1"/>
-      <c r="I126" s="14" t="s">
+      <c r="I126" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J126" s="1"/>
@@ -20282,7 +20273,7 @@
       <c r="AG126" s="1">
         <v>0</v>
       </c>
-      <c r="AH126" s="16" t="s">
+      <c r="AH126" s="15" t="s">
         <v>178</v>
       </c>
       <c r="AI126" s="1">
@@ -20327,7 +20318,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="H127" s="1"/>
-      <c r="I127" s="14" t="s">
+      <c r="I127" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J127" s="1"/>
@@ -20394,7 +20385,7 @@
       <c r="AG127" s="1">
         <v>0</v>
       </c>
-      <c r="AH127" s="16" t="s">
+      <c r="AH127" s="15" t="s">
         <v>178</v>
       </c>
       <c r="AI127" s="1">
@@ -20543,7 +20534,7 @@
       <c r="H129" s="1">
         <v>40</v>
       </c>
-      <c r="I129" s="14" t="s">
+      <c r="I129" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J129" s="1"/>
@@ -20655,7 +20646,7 @@
       <c r="H130" s="1">
         <v>40</v>
       </c>
-      <c r="I130" s="14" t="s">
+      <c r="I130" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J130" s="1"/>
@@ -20882,7 +20873,7 @@
       <c r="H132" s="1">
         <v>40</v>
       </c>
-      <c r="I132" s="14" t="s">
+      <c r="I132" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J132" s="1"/>
@@ -20994,7 +20985,7 @@
       <c r="H133" s="1">
         <v>45</v>
       </c>
-      <c r="I133" s="14" t="s">
+      <c r="I133" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J133" s="1"/>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/27,08,26 ПОКОМ КИ/дв 27,08,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/27,08,26 ПОКОМ КИ/дв 27,08,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\27,08,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\27,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBA001A-4F3F-425D-9ABD-187561BCED44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77617729-CB85-4633-952B-602EA1E963A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$134</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -792,7 +800,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
